--- a/employes_securise.xlsx
+++ b/employes_securise.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -532,6 +532,41 @@
       <c r="G3" t="inlineStr">
         <is>
           <t>2025-08-21 21:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Mihary</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Gino</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>gAAAAABop2KGhvxLfyRNtdYnG08GMLROMqQizgo9-udoBdz2PlVU0rhtz0kXdhIU7PClnghhLAeDynLzTonmD1bclV2zvayxhg==</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>gAAAAABop2KGWS5g_g48HUVNV0ml-0OO2ixEFw_EU94gqkFrTBr4-J3MTs40SkNq2yDBepzgi33zFrSl0dJ9WkP9MVef2RP7bQ==</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>gAAAAABop2KGFecAonalOYn1EYYJarPhAeHtGaq2oinGSDelnwZn4_nRt4Gj4jOvxoBQ1Y4GnTtnOm4ws30LvBN-cTWJ1ZDY7g==</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2025-08-21 21:16</t>
         </is>
       </c>
     </row>
